--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:30+00:00</t>
+    <t>2025-05-13T11:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:53:59+00:00</t>
+    <t>2025-05-13T11:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:54:01+00:00</t>
+    <t>2025-05-14T06:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:38+00:00</t>
+    <t>2025-05-14T06:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:56:25+00:00</t>
+    <t>2025-05-14T07:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:16+00:00</t>
+    <t>2025-05-14T07:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:52:33+00:00</t>
+    <t>2025-05-14T07:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:53:22+00:00</t>
+    <t>2025-05-14T15:00:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:00:45+00:00</t>
+    <t>2025-05-22T14:06:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:43:01+00:00</t>
+    <t>2025-05-22T14:52:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:52:21+00:00</t>
+    <t>2025-06-11T04:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T04:00:37+00:00</t>
+    <t>2025-06-26T13:57:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-26T13:57:34+00:00</t>
+    <t>2025-07-16T16:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
+++ b/branches/master/StructureDefinition-PSSQuestionnaireTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T16:47:23+00:00</t>
+    <t>2025-07-16T16:49:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
